--- a/docs/data/afts-recalls-public.xlsx
+++ b/docs/data/afts-recalls-public.xlsx
@@ -81220,7 +81220,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-30 03:01 UTC</t>
+          <t>Generated: 2026-07-30 21:02 UTC</t>
         </is>
       </c>
     </row>
